--- a/output/pdf_financials_xlsx/SBC.xlsx
+++ b/output/pdf_financials_xlsx/SBC.xlsx
@@ -894,25 +894,25 @@
         <v>1.736101</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.00377</v>
+        <v>1.593382</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.946717</v>
+        <v>1.53916</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.118234</v>
+        <v>2.160416</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.133813</v>
+        <v>1.814051</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.026115</v>
+        <v>2.069206</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.775997</v>
+        <v>2.657607</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.938307</v>
+        <v>5.462668</v>
       </c>
     </row>
     <row r="11">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002603</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001272</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012569</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.015229</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-52.107205</v>
+        <v>-52.109808</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>51.23536</v>
+        <v>51.234088</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.507831</v>
+        <v>7.495262</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.91548</v>
+        <v>-0.930709</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.96806</v>
+        <v>12.96676</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>25.693368</v>
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-52.107205</v>
+        <v>-52.109808</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>51.23536</v>
+        <v>51.234088</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.507831</v>
+        <v>7.495262</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.91548</v>
+        <v>-0.930709</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.96806</v>
+        <v>12.96676</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>25.693368</v>
@@ -2330,31 +2330,31 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.179312</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.566222</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.437243</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.277522</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.73943</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.155307</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.289968</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.591486</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.475051</v>
       </c>
     </row>
     <row r="35">
@@ -2428,31 +2428,31 @@
         <v>0.179312</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.384211</v>
+        <v>0.563523</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.566222</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.437243</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.277522</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.73943</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.155307</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.289968</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.591486</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.475051</v>
       </c>
     </row>
     <row r="37">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -39296,7 +39296,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -42046,7 +42046,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" s="5" t="n">

--- a/output/pdf_financials_xlsx/SBC.xlsx
+++ b/output/pdf_financials_xlsx/SBC.xlsx
@@ -39370,7 +39370,11 @@
           <t>Net investment income (loss) before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -39442,7 +39446,11 @@
           <t>Distributions on Preferred shares (note 6)</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -40566,7 +40574,11 @@
           <t>Distributions on Preferred shares (note 7)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E403" s="5" t="n">
         <v>-3.563957</v>
       </c>
@@ -41638,7 +41650,11 @@
           <t>Net investment income before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -43818,7 +43834,11 @@
           <t>Distributions on Preferred shares (note 8)</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
